--- a/Result/profitability/5426.xlsx
+++ b/Result/profitability/5426.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,16 +669,16 @@
         <v>0.27</v>
       </c>
       <c r="M2" t="n">
-        <v>0.24375</v>
+        <v>0.1875</v>
       </c>
       <c r="N2" t="n">
-        <v>19.67</v>
+        <v>20.175</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -687,7 +687,7 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.59</v>
       </c>
       <c r="M3" t="n">
-        <v>0.24625</v>
+        <v>0.22125</v>
       </c>
       <c r="N3" t="n">
-        <v>19.82375</v>
+        <v>19.3675</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.53</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2725</v>
+        <v>0.2375</v>
       </c>
       <c r="N4" t="n">
-        <v>18.47125</v>
+        <v>18.13375</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.49</v>
       </c>
       <c r="M5" t="n">
-        <v>0.28375</v>
+        <v>0.31375</v>
       </c>
       <c r="N5" t="n">
-        <v>18.1475</v>
+        <v>18.3725</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1042,7 +1042,7 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" t="n">
         <v>97.40000000000001</v>
@@ -1137,10 +1137,10 @@
         <v>0.52</v>
       </c>
       <c r="M6" t="n">
-        <v>0.36375</v>
+        <v>0.365</v>
       </c>
       <c r="N6" t="n">
-        <v>18.2475</v>
+        <v>18.83</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1267,7 +1267,7 @@
         <v>0.4</v>
       </c>
       <c r="N7" t="n">
-        <v>20.99875</v>
+        <v>21.65875</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.57</v>
       </c>
       <c r="M8" t="n">
-        <v>0.45625</v>
+        <v>0.43625</v>
       </c>
       <c r="N8" t="n">
-        <v>22.25375</v>
+        <v>22.29625</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9834,6 +9834,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5426</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>504</v>
+      </c>
+      <c r="D75" t="n">
+        <v>397</v>
+      </c>
+      <c r="E75" t="n">
+        <v>108</v>
+      </c>
+      <c r="F75" t="n">
+        <v>21.34</v>
+      </c>
+      <c r="G75" t="n">
+        <v>33</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>6.57%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J75" t="n">
+        <v>32</v>
+      </c>
+      <c r="K75" t="n">
+        <v>17</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.225</v>
+      </c>
+      <c r="N75" t="n">
+        <v>20.11875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.5714285714285715</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.3399999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.01619047619047609</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>1.800000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.09211873080859778</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
